--- a/cave_monster_cards.xlsx
+++ b/cave_monster_cards.xlsx
@@ -33,7 +33,7 @@
     <t>Scrape</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1 Damage to each Adventurer.</t>
+    <t xml:space="preserve">Deal 2 Damage to each Adventurer.</t>
   </si>
   <si>
     <t>cardimages/echo.png</t>
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Tight Squeeze</t>
   </si>
   <si>
-    <t xml:space="preserve">Adventurers must choose: lose any 2 resources, take 1 unpreventable damage, or discard 2 cards.</t>
+    <t xml:space="preserve">Adventurers must choose: lose any 2 resources, take 2 unpreventable damage, or discard 2 cards.</t>
   </si>
   <si>
     <t>cardimages/starvation.png</t>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Narrow Sights</t>
   </si>
   <si>
-    <t xml:space="preserve">Prevent 1 Damage for each Adventurer in the party.</t>
+    <t xml:space="preserve">Prevent 2 Damage for each Adventurer in the party.</t>
   </si>
   <si>
     <t>cardimages/cave_maze.png</t>
@@ -96,7 +96,7 @@
     <t>Fungus</t>
   </si>
   <si>
-    <t xml:space="preserve">Place below monster track. Take 1 damage each turn until resources equal to number of Adventurers are discarded.</t>
+    <t xml:space="preserve">Place below monster track. Take 2 damage each turn until resources equal to number of Adventurers are discarded.</t>
   </si>
   <si>
     <t>cardimages/bat_swarm.png</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Bat Swarm</t>
   </si>
   <si>
-    <t xml:space="preserve">Each player takes 1 preventable damage; monster heals for the unprevented amount.</t>
+    <t xml:space="preserve">Each player takes 2 preventable damage; monster heals for the unprevented amount.</t>
   </si>
   <si>
     <t>cardimages/quiet_dead_end.png</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Quiet Dead End</t>
   </si>
   <si>
-    <t xml:space="preserve">Every Adventurer may heal 2 health.</t>
+    <t xml:space="preserve">Every Adventurer may heal 4 health.</t>
   </si>
 </sst>
 </file>
